--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5441,6 +5441,725 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>118970344</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91798</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>459773</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6864317</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>118970248</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>459807</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6864187</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På kolbotten.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>118970206</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91798</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>459768</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6864215</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>118970157</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78227</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>459817</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6864172</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>118970679</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91798</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>459803</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6864527</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>118970438</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91412</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>459589</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6864328</v>
+      </c>
+      <c r="S49" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>118970354</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91798</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>459784</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6864314</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -5443,7 +5443,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118970344</v>
+        <v>118970354</v>
       </c>
       <c r="B44" t="n">
         <v>91798</v>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459773</v>
+        <v>459784</v>
       </c>
       <c r="R44" t="n">
-        <v>6864317</v>
+        <v>6864314</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5545,10 +5545,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118970248</v>
+        <v>118970206</v>
       </c>
       <c r="B45" t="n">
-        <v>91780</v>
+        <v>91798</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5557,25 +5557,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459807</v>
+        <v>459768</v>
       </c>
       <c r="R45" t="n">
-        <v>6864187</v>
+        <v>6864215</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5621,11 +5621,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På kolbotten.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5652,7 +5647,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118970206</v>
+        <v>118970344</v>
       </c>
       <c r="B46" t="n">
         <v>91798</v>
@@ -5692,10 +5687,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459768</v>
+        <v>459773</v>
       </c>
       <c r="R46" t="n">
-        <v>6864215</v>
+        <v>6864317</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5754,10 +5749,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118970157</v>
+        <v>118970679</v>
       </c>
       <c r="B47" t="n">
-        <v>78227</v>
+        <v>91798</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5766,25 +5761,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5794,10 +5789,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459817</v>
+        <v>459803</v>
       </c>
       <c r="R47" t="n">
-        <v>6864172</v>
+        <v>6864527</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5856,10 +5851,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118970679</v>
+        <v>118970157</v>
       </c>
       <c r="B48" t="n">
-        <v>91798</v>
+        <v>78227</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5868,25 +5863,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5896,10 +5891,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459803</v>
+        <v>459817</v>
       </c>
       <c r="R48" t="n">
-        <v>6864527</v>
+        <v>6864172</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -6060,10 +6055,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118970354</v>
+        <v>118970248</v>
       </c>
       <c r="B50" t="n">
-        <v>91798</v>
+        <v>91780</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6072,25 +6067,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6100,10 +6095,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459784</v>
+        <v>459807</v>
       </c>
       <c r="R50" t="n">
-        <v>6864314</v>
+        <v>6864187</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6136,6 +6131,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På kolbotten.</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -5446,11 +5446,11 @@
         <v>118970248</v>
       </c>
       <c r="B44" t="n">
-        <v>91803</v>
+        <v>91998</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5479,7 +5479,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -5446,7 +5446,7 @@
         <v>118970248</v>
       </c>
       <c r="B44" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -5446,7 +5446,7 @@
         <v>118970248</v>
       </c>
       <c r="B44" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -5446,7 +5446,7 @@
         <v>118970248</v>
       </c>
       <c r="B44" t="n">
-        <v>92014</v>
+        <v>92015</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -5446,7 +5446,7 @@
         <v>118970248</v>
       </c>
       <c r="B44" t="n">
-        <v>92015</v>
+        <v>92024</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3945,10 +3945,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96205253</v>
+        <v>125128236</v>
       </c>
       <c r="B31" t="n">
-        <v>90653</v>
+        <v>78546</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3957,44 +3957,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnbergsmyren, Härjåsjön, Lillhärdal, Hjd</t>
+          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459688.7567071787</v>
+        <v>460512</v>
       </c>
       <c r="R31" t="n">
-        <v>6864622.355141696</v>
+        <v>6864017</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4018,27 +4015,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar på och i anslutning till viltstig</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4047,89 +4029,71 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>sandtallskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96205216</v>
+        <v>125128290</v>
       </c>
       <c r="B32" t="n">
-        <v>91628</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kvarnbergsmyren, Härjåsjön, Lillhärdal, Hjd</t>
+          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459807</v>
+        <v>460601</v>
       </c>
       <c r="R32" t="n">
-        <v>6864565</v>
+        <v>6864036</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4153,12 +4117,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,39 +4131,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>sandtallskog</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>96205090</v>
+        <v>125128001</v>
       </c>
       <c r="B33" t="n">
-        <v>90653</v>
+        <v>98018</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4212,44 +4165,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kvarnbergsmyren, Härjåsjön, Lillhärdal, Hjd</t>
+          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459823.5260811325</v>
+        <v>460401</v>
       </c>
       <c r="R33" t="n">
-        <v>6864805.944428221</v>
+        <v>6863944</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4273,27 +4219,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i laven</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,29 +4233,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>98951687</v>
+        <v>125127968</v>
       </c>
       <c r="B34" t="n">
-        <v>76486</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4333,42 +4263,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Härjåsjön, Hjd</t>
+          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459662.1383821564</v>
+        <v>460398</v>
       </c>
       <c r="R34" t="n">
-        <v>6864606.177517666</v>
+        <v>6863946</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4392,22 +4330,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4434,10 +4362,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>98951677</v>
+        <v>96205253</v>
       </c>
       <c r="B35" t="n">
-        <v>76909</v>
+        <v>90653</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4446,39 +4374,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Härjåsjön , Hjd</t>
+          <t>Kvarnbergsmyren, Härjåsjön, Lillhärdal, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459692.2506225323</v>
+        <v>459688.7567071787</v>
       </c>
       <c r="R35" t="n">
-        <v>6864358.898972569</v>
+        <v>6864622.355141696</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4505,7 +4435,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -4515,7 +4445,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -4523,38 +4453,54 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på och i anslutning till viltstig</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>100711294</v>
+        <v>96205216</v>
       </c>
       <c r="B36" t="n">
-        <v>78569</v>
+        <v>91628</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4563,37 +4509,44 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Kvarnbergsmyren, Härjåsjön, Lillhärdal, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459713.0093013519</v>
+        <v>459807</v>
       </c>
       <c r="R36" t="n">
-        <v>6864997.60001069</v>
+        <v>6864565</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4617,22 +4570,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4641,28 +4584,39 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>100711287</v>
+        <v>96205090</v>
       </c>
       <c r="B37" t="n">
-        <v>77259</v>
+        <v>90653</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4671,41 +4625,48 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Kvarnbergsmyren, Härjåsjön, Lillhärdal, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459787.0113399865</v>
+        <v>459823.5260811325</v>
       </c>
       <c r="R37" t="n">
-        <v>6864590.56685351</v>
+        <v>6864805.944428221</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4729,7 +4690,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4739,7 +4700,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -4747,34 +4708,40 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i laven</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>100711263</v>
+        <v>98951687</v>
       </c>
       <c r="B38" t="n">
-        <v>78098</v>
+        <v>76486</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4787,37 +4754,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459735.9482922081</v>
+        <v>459662.1383821564</v>
       </c>
       <c r="R38" t="n">
-        <v>6864942.203522061</v>
+        <v>6864606.177517666</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4841,7 +4809,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -4851,7 +4819,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -4871,22 +4839,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>100711275</v>
+        <v>98951677</v>
       </c>
       <c r="B39" t="n">
-        <v>56540</v>
+        <v>76909</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4899,37 +4867,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459931.2134978434</v>
+        <v>459692.2506225323</v>
       </c>
       <c r="R39" t="n">
-        <v>6864010.645513522</v>
+        <v>6864358.898972569</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4953,7 +4922,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -4963,7 +4932,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -4983,22 +4952,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>100711276</v>
+        <v>100711294</v>
       </c>
       <c r="B40" t="n">
-        <v>56540</v>
+        <v>78569</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5011,21 +4980,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5035,10 +5004,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459695.4964385364</v>
+        <v>459713.0093013519</v>
       </c>
       <c r="R40" t="n">
-        <v>6864473.842062026</v>
+        <v>6864997.60001069</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5107,7 +5076,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>100711286</v>
+        <v>100711287</v>
       </c>
       <c r="B41" t="n">
         <v>77259</v>
@@ -5147,10 +5116,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459735.9316082247</v>
+        <v>459787.0113399865</v>
       </c>
       <c r="R41" t="n">
-        <v>6864940.790230161</v>
+        <v>6864590.56685351</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5219,10 +5188,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>100711320</v>
+        <v>100711263</v>
       </c>
       <c r="B42" t="n">
-        <v>93868</v>
+        <v>78098</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5231,25 +5200,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5259,10 +5228,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459837.8383123052</v>
+        <v>459735.9482922081</v>
       </c>
       <c r="R42" t="n">
-        <v>6864538.60567635</v>
+        <v>6864942.203522061</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5331,10 +5300,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>100711266</v>
+        <v>100711275</v>
       </c>
       <c r="B43" t="n">
-        <v>78072</v>
+        <v>56540</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5347,21 +5316,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5371,10 +5340,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459784.8725669582</v>
+        <v>459931.2134978434</v>
       </c>
       <c r="R43" t="n">
-        <v>6865089.568225338</v>
+        <v>6864010.645513522</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5443,14 +5412,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118970248</v>
+        <v>100711276</v>
       </c>
       <c r="B44" t="n">
-        <v>92024</v>
+        <v>56540</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5459,37 +5428,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Härjåsjön , Härjåsjön , Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459807</v>
+        <v>459695.4964385364</v>
       </c>
       <c r="R44" t="n">
-        <v>6864187</v>
+        <v>6864473.842062026</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5513,17 +5482,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På kolbotten.</t>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5538,22 +5512,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118970344</v>
+        <v>100711286</v>
       </c>
       <c r="B45" t="n">
-        <v>91821</v>
+        <v>77259</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5562,41 +5536,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459773</v>
+        <v>459735.9316082247</v>
       </c>
       <c r="R45" t="n">
-        <v>6864317</v>
+        <v>6864940.790230161</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5620,12 +5594,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5640,22 +5624,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118970206</v>
+        <v>100711320</v>
       </c>
       <c r="B46" t="n">
-        <v>91821</v>
+        <v>93868</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5668,37 +5652,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4366</v>
+        <v>2869</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459768</v>
+        <v>459837.8383123052</v>
       </c>
       <c r="R46" t="n">
-        <v>6864215</v>
+        <v>6864538.60567635</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5722,12 +5706,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5742,22 +5736,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118970679</v>
+        <v>100711266</v>
       </c>
       <c r="B47" t="n">
-        <v>91821</v>
+        <v>78072</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5766,41 +5760,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459803</v>
+        <v>459784.8725669582</v>
       </c>
       <c r="R47" t="n">
-        <v>6864527</v>
+        <v>6865089.568225338</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5824,12 +5818,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5844,26 +5848,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118970157</v>
+        <v>118970248</v>
       </c>
       <c r="B48" t="n">
-        <v>78247</v>
+        <v>92024</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5872,34 +5876,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459817</v>
+        <v>459807</v>
       </c>
       <c r="R48" t="n">
-        <v>6864172</v>
+        <v>6864187</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5932,6 +5936,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På kolbotten.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5958,10 +5967,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118970438</v>
+        <v>118970344</v>
       </c>
       <c r="B49" t="n">
-        <v>91432</v>
+        <v>91821</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5970,25 +5979,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5998,10 +6007,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459589</v>
+        <v>459773</v>
       </c>
       <c r="R49" t="n">
-        <v>6864328</v>
+        <v>6864317</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6060,7 +6069,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118970354</v>
+        <v>118970206</v>
       </c>
       <c r="B50" t="n">
         <v>91821</v>
@@ -6100,10 +6109,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459784</v>
+        <v>459768</v>
       </c>
       <c r="R50" t="n">
-        <v>6864314</v>
+        <v>6864215</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6159,6 +6168,414 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>118970679</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91821</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>459803</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6864527</v>
+      </c>
+      <c r="S51" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>118970157</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78247</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>459817</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6864172</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>118970438</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91432</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>459589</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6864328</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>118970354</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91821</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>459784</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6864314</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -3945,10 +3945,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125128236</v>
+        <v>125127968</v>
       </c>
       <c r="B31" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3957,38 +3957,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460512</v>
+        <v>460398</v>
       </c>
       <c r="R31" t="n">
-        <v>6864017</v>
+        <v>6863946</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4149,10 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125128001</v>
+        <v>125128236</v>
       </c>
       <c r="B33" t="n">
-        <v>98018</v>
+        <v>78546</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4161,25 +4170,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4189,13 +4198,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460401</v>
+        <v>460512</v>
       </c>
       <c r="R33" t="n">
-        <v>6863944</v>
+        <v>6864017</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4251,10 +4260,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125127968</v>
+        <v>125128001</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>98018</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4263,50 +4272,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460398</v>
+        <v>460401</v>
       </c>
       <c r="R34" t="n">
-        <v>6863946</v>
+        <v>6863944</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -4158,10 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125128236</v>
+        <v>125128001</v>
       </c>
       <c r="B33" t="n">
-        <v>78546</v>
+        <v>98018</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4170,25 +4170,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4198,13 +4198,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460512</v>
+        <v>460401</v>
       </c>
       <c r="R33" t="n">
-        <v>6864017</v>
+        <v>6863944</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125128001</v>
+        <v>125128236</v>
       </c>
       <c r="B34" t="n">
-        <v>98018</v>
+        <v>78546</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4272,25 +4272,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460401</v>
+        <v>460512</v>
       </c>
       <c r="R34" t="n">
-        <v>6863944</v>
+        <v>6864017</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -3945,10 +3945,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125127968</v>
+        <v>125128001</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>98018</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3957,50 +3957,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460398</v>
+        <v>460401</v>
       </c>
       <c r="R31" t="n">
-        <v>6863946</v>
+        <v>6863944</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4158,10 +4149,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125128001</v>
+        <v>125128236</v>
       </c>
       <c r="B33" t="n">
-        <v>98018</v>
+        <v>78546</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4170,25 +4161,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4198,13 +4189,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460401</v>
+        <v>460512</v>
       </c>
       <c r="R33" t="n">
-        <v>6863944</v>
+        <v>6864017</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4260,10 +4251,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125128236</v>
+        <v>125127968</v>
       </c>
       <c r="B34" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4272,38 +4263,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460512</v>
+        <v>460398</v>
       </c>
       <c r="R34" t="n">
-        <v>6864017</v>
+        <v>6863946</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -4047,10 +4047,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125128290</v>
+        <v>125128236</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4059,25 +4059,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460601</v>
+        <v>460512</v>
       </c>
       <c r="R32" t="n">
-        <v>6864036</v>
+        <v>6864017</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125128236</v>
+        <v>125128290</v>
       </c>
       <c r="B33" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4161,25 +4161,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460512</v>
+        <v>460601</v>
       </c>
       <c r="R33" t="n">
-        <v>6864017</v>
+        <v>6864036</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -3945,10 +3945,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125128001</v>
+        <v>125128290</v>
       </c>
       <c r="B31" t="n">
-        <v>98018</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3957,25 +3957,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460401</v>
+        <v>460601</v>
       </c>
       <c r="R31" t="n">
-        <v>6863944</v>
+        <v>6864036</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4047,10 +4047,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125128236</v>
+        <v>125127968</v>
       </c>
       <c r="B32" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4059,38 +4059,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460512</v>
+        <v>460398</v>
       </c>
       <c r="R32" t="n">
-        <v>6864017</v>
+        <v>6863946</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4149,10 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125128290</v>
+        <v>125128236</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4161,25 +4170,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4189,10 +4198,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460601</v>
+        <v>460512</v>
       </c>
       <c r="R33" t="n">
-        <v>6864036</v>
+        <v>6864017</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4251,10 +4260,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125127968</v>
+        <v>125128001</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>98018</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4263,50 +4272,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460398</v>
+        <v>460401</v>
       </c>
       <c r="R34" t="n">
-        <v>6863946</v>
+        <v>6863944</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -3945,7 +3945,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125128290</v>
+        <v>125127968</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3978,17 +3978,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460601</v>
+        <v>460398</v>
       </c>
       <c r="R31" t="n">
-        <v>6864036</v>
+        <v>6863946</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4047,10 +4056,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125127968</v>
+        <v>125128236</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4059,47 +4068,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460398</v>
+        <v>460512</v>
       </c>
       <c r="R32" t="n">
-        <v>6863946</v>
+        <v>6864017</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125128236</v>
+        <v>125128290</v>
       </c>
       <c r="B33" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4170,25 +4170,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460512</v>
+        <v>460601</v>
       </c>
       <c r="R33" t="n">
-        <v>6864017</v>
+        <v>6864036</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -4056,10 +4056,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125128236</v>
+        <v>125128001</v>
       </c>
       <c r="B32" t="n">
-        <v>78546</v>
+        <v>98018</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4068,25 +4068,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4096,13 +4096,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460512</v>
+        <v>460401</v>
       </c>
       <c r="R32" t="n">
-        <v>6864017</v>
+        <v>6863944</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125128001</v>
+        <v>125128236</v>
       </c>
       <c r="B34" t="n">
-        <v>98018</v>
+        <v>78546</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4272,25 +4272,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460401</v>
+        <v>460512</v>
       </c>
       <c r="R34" t="n">
-        <v>6863944</v>
+        <v>6864017</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -3948,7 +3948,7 @@
         <v>125127968</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4056,10 +4056,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125128001</v>
+        <v>125128290</v>
       </c>
       <c r="B32" t="n">
-        <v>98018</v>
+        <v>98269</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4068,25 +4068,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4096,13 +4096,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460401</v>
+        <v>460601</v>
       </c>
       <c r="R32" t="n">
-        <v>6863944</v>
+        <v>6864036</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125128290</v>
+        <v>125128236</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>78683</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4170,25 +4170,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460601</v>
+        <v>460512</v>
       </c>
       <c r="R33" t="n">
-        <v>6864036</v>
+        <v>6864017</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125128236</v>
+        <v>125128001</v>
       </c>
       <c r="B34" t="n">
-        <v>78546</v>
+        <v>98186</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4272,25 +4272,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460512</v>
+        <v>460401</v>
       </c>
       <c r="R34" t="n">
-        <v>6864017</v>
+        <v>6863944</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -3945,7 +3945,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125127968</v>
+        <v>125128290</v>
       </c>
       <c r="B31" t="n">
         <v>98269</v>
@@ -3978,26 +3978,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460398</v>
+        <v>460601</v>
       </c>
       <c r="R31" t="n">
-        <v>6863946</v>
+        <v>6864036</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4056,7 +4047,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125128290</v>
+        <v>125127968</v>
       </c>
       <c r="B32" t="n">
         <v>98269</v>
@@ -4089,17 +4080,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460601</v>
+        <v>460398</v>
       </c>
       <c r="R32" t="n">
-        <v>6864036</v>
+        <v>6863946</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -3945,37 +3945,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125128290</v>
+        <v>125128236</v>
       </c>
       <c r="B31" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3985,10 +3980,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460601</v>
+        <v>460512</v>
       </c>
       <c r="R31" t="n">
-        <v>6864036</v>
+        <v>6864017</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4050,12 +4045,7 @@
         <v>125127968</v>
       </c>
       <c r="B32" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4158,37 +4148,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125128236</v>
+        <v>125128001</v>
       </c>
       <c r="B33" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98241</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4198,13 +4183,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460512</v>
+        <v>460401</v>
       </c>
       <c r="R33" t="n">
-        <v>6864017</v>
+        <v>6863944</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4260,37 +4245,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125128001</v>
+        <v>125128290</v>
       </c>
       <c r="B34" t="n">
-        <v>98186</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4300,13 +4280,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460401</v>
+        <v>460601</v>
       </c>
       <c r="R34" t="n">
-        <v>6863944</v>
+        <v>6864036</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 38362-2021 artfynd.xlsx
+++ b/artfynd/A 38362-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100711302</v>
+        <v>100711317</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460654.7670103617</v>
+        <v>460532</v>
       </c>
       <c r="R2" t="n">
-        <v>6864418.819088018</v>
+        <v>6864082</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,19 +743,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>100711313</v>
       </c>
       <c r="B3" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460532.4187673989</v>
+        <v>460532</v>
       </c>
       <c r="R3" t="n">
-        <v>6864082.342507601</v>
+        <v>6864082</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -860,19 +840,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100711267</v>
+        <v>100711277</v>
       </c>
       <c r="B4" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460326.8591907343</v>
+        <v>460374</v>
       </c>
       <c r="R4" t="n">
-        <v>6864101.692563338</v>
+        <v>6864107</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -972,19 +937,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +969,7 @@
         <v>100711280</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460619.8761643572</v>
+        <v>460620</v>
       </c>
       <c r="R5" t="n">
-        <v>6864094.527701702</v>
+        <v>6864094</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1084,19 +1034,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100711308</v>
+        <v>100711281</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460450.806194155</v>
+        <v>460107</v>
       </c>
       <c r="R6" t="n">
-        <v>6864045.113792237</v>
+        <v>6863977</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1196,19 +1131,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,53 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100711300</v>
+        <v>125127563</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460438.904586618</v>
+        <v>460360</v>
       </c>
       <c r="R7" t="n">
-        <v>6864361.939801192</v>
+        <v>6863908</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,65 +1245,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100711312</v>
+        <v>125127623</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460663.8684181016</v>
+        <v>460398</v>
       </c>
       <c r="R8" t="n">
-        <v>6864430.494897602</v>
+        <v>6863919</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,31 +1342,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100711316</v>
+        <v>100711314</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460099.4830133786</v>
+        <v>460655</v>
       </c>
       <c r="R9" t="n">
-        <v>6863990.764491933</v>
+        <v>6864148</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1532,19 +1422,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100711310</v>
+        <v>100711315</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460454.9497457169</v>
+        <v>460368</v>
       </c>
       <c r="R10" t="n">
-        <v>6864036.111362247</v>
+        <v>6864132</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1644,19 +1519,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100711299</v>
+        <v>100711316</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460486.8232600313</v>
+        <v>460100</v>
       </c>
       <c r="R11" t="n">
-        <v>6864261.48010377</v>
+        <v>6863991</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1756,19 +1616,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100711295</v>
+        <v>100711297</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460619.8761643572</v>
+        <v>460380</v>
       </c>
       <c r="R12" t="n">
-        <v>6864094.527701702</v>
+        <v>6864313</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1868,19 +1713,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100711304</v>
+        <v>100711298</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460583.3528398316</v>
+        <v>460327</v>
       </c>
       <c r="R13" t="n">
-        <v>6864323.982115888</v>
+        <v>6864101</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1980,19 +1810,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>100711297</v>
+        <v>125128236</v>
       </c>
       <c r="B14" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,17 +1870,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460379.3449127805</v>
+        <v>460512</v>
       </c>
       <c r="R14" t="n">
-        <v>6864313.150413959</v>
+        <v>6864017</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,22 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,49 +1924,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>100711306</v>
+        <v>100711295</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460628.3695274559</v>
+        <v>460620</v>
       </c>
       <c r="R15" t="n">
-        <v>6864053.42839745</v>
+        <v>6864094</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2204,19 +2004,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>100711291</v>
+        <v>125127598</v>
       </c>
       <c r="B16" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,37 +2044,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460574.1328177813</v>
+        <v>460389</v>
       </c>
       <c r="R16" t="n">
-        <v>6864097.883645031</v>
+        <v>6863912</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2313,22 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,49 +2118,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>100711288</v>
+        <v>100711272</v>
       </c>
       <c r="B17" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460344.6434489273</v>
+        <v>460732</v>
       </c>
       <c r="R17" t="n">
-        <v>6864372.930228422</v>
+        <v>6864428</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2428,19 +2198,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,53 +2227,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>100711281</v>
+        <v>125128001</v>
       </c>
       <c r="B18" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460106.8741511818</v>
+        <v>460401</v>
       </c>
       <c r="R18" t="n">
-        <v>6863977.010556689</v>
+        <v>6863944</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2537,22 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,27 +2312,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>100711311</v>
+        <v>100711299</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460441.3151358742</v>
+        <v>460487</v>
       </c>
       <c r="R19" t="n">
-        <v>6863999.980283059</v>
+        <v>6864262</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2652,19 +2392,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>100711292</v>
+        <v>100711300</v>
       </c>
       <c r="B20" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460372.5846375168</v>
+        <v>460439</v>
       </c>
       <c r="R20" t="n">
-        <v>6864137.449251003</v>
+        <v>6864362</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2764,19 +2489,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>100711277</v>
+        <v>100711301</v>
       </c>
       <c r="B21" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460374.1220274236</v>
+        <v>460438</v>
       </c>
       <c r="R21" t="n">
-        <v>6864107.269898937</v>
+        <v>6864392</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2876,19 +2586,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>100711301</v>
+        <v>100711302</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460437.3667726308</v>
+        <v>460655</v>
       </c>
       <c r="R22" t="n">
-        <v>6864392.116871623</v>
+        <v>6864419</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2988,19 +2683,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,37 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>100711315</v>
+        <v>100711304</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460367.8053080226</v>
+        <v>460583</v>
       </c>
       <c r="R23" t="n">
-        <v>6864132.320777359</v>
+        <v>6864324</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3100,19 +2780,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,37 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>100711293</v>
+        <v>100711305</v>
       </c>
       <c r="B24" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460326.8591907343</v>
+        <v>460661</v>
       </c>
       <c r="R24" t="n">
-        <v>6864101.692563338</v>
+        <v>6864145</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3212,19 +2877,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,37 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>100711289</v>
+        <v>100711306</v>
       </c>
       <c r="B25" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460379.3449127805</v>
+        <v>460629</v>
       </c>
       <c r="R25" t="n">
-        <v>6864313.150413959</v>
+        <v>6864054</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3324,19 +2974,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,37 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>100711317</v>
+        <v>100711308</v>
       </c>
       <c r="B26" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460532.4187673989</v>
+        <v>460451</v>
       </c>
       <c r="R26" t="n">
-        <v>6864082.342507601</v>
+        <v>6864045</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3436,19 +3071,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,37 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>100711298</v>
+        <v>100711310</v>
       </c>
       <c r="B27" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460326.8591907343</v>
+        <v>460455</v>
       </c>
       <c r="R27" t="n">
-        <v>6864101.692563338</v>
+        <v>6864036</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3548,19 +3168,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>102963579</v>
+        <v>100711311</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3620,30 +3225,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Digerbäcken Härjåsjön, Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460514.6683205088</v>
+        <v>460441</v>
       </c>
       <c r="R28" t="n">
-        <v>6864139.100820702</v>
+        <v>6864000</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3667,22 +3262,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3697,27 +3282,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>102963586</v>
+        <v>100711312</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3743,21 +3323,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Digerbäcken Härjåsjön, Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460546.7768105627</v>
+        <v>460664</v>
       </c>
       <c r="R29" t="n">
-        <v>6864181.143453513</v>
+        <v>6864431</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3781,22 +3359,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,12 +3379,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3826,12 +3394,7 @@
         <v>102963564</v>
       </c>
       <c r="B30" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3873,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460512.2186147226</v>
+        <v>460512</v>
       </c>
       <c r="R30" t="n">
-        <v>6864172.117952689</v>
+        <v>6864172</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3906,19 +3469,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3945,48 +3498,58 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125128236</v>
+        <v>102963579</v>
       </c>
       <c r="B31" t="n">
-        <v>78725</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
+          <t>Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460512</v>
+        <v>460514</v>
       </c>
       <c r="R31" t="n">
-        <v>6864017</v>
+        <v>6864139</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4010,12 +3573,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,10 +3605,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125127968</v>
+        <v>102963586</v>
       </c>
       <c r="B32" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4070,29 +3633,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
+          <t>Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460398</v>
+        <v>460547</v>
       </c>
       <c r="R32" t="n">
-        <v>6863946</v>
+        <v>6864181</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4116,12 +3672,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4148,48 +3704,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125128001</v>
+        <v>125127968</v>
       </c>
       <c r="B33" t="n">
-        <v>98241</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460401</v>
+        <v>460398</v>
       </c>
       <c r="R33" t="n">
-        <v>6863944</v>
+        <v>6863946</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4248,7 +3813,7 @@
         <v>125128290</v>
       </c>
       <c r="B34" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4342,56 +3907,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96205253</v>
+        <v>100711288</v>
       </c>
       <c r="B35" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kvarnbergsmyren, Härjåsjön, Lillhärdal, Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459688.7567071787</v>
+        <v>460345</v>
       </c>
       <c r="R35" t="n">
-        <v>6864622.355141696</v>
+        <v>6864373</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4415,27 +3972,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar på och i anslutning till viltstig</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4444,44 +3986,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>sandtallskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>96205216</v>
+        <v>100711289</v>
       </c>
       <c r="B36" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4489,44 +4015,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnbergsmyren, Härjåsjön, Lillhärdal, Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459807</v>
+        <v>460380</v>
       </c>
       <c r="R36" t="n">
-        <v>6864565</v>
+        <v>6864313</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4550,12 +4069,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4564,89 +4083,66 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>sandtallskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>96205090</v>
+        <v>100711290</v>
       </c>
       <c r="B37" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnbergsmyren, Härjåsjön, Lillhärdal, Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459823.5260811325</v>
+        <v>460652</v>
       </c>
       <c r="R37" t="n">
-        <v>6864805.944428221</v>
+        <v>6864165</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4670,27 +4166,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i laven</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4699,34 +4180,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>98951687</v>
+        <v>100711291</v>
       </c>
       <c r="B38" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,38 +4209,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Härjåsjön, Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459662.1383821564</v>
+        <v>460574</v>
       </c>
       <c r="R38" t="n">
-        <v>6864606.177517666</v>
+        <v>6864098</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4789,22 +4263,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,27 +4283,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>98951677</v>
+        <v>100711292</v>
       </c>
       <c r="B39" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4847,38 +4306,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Härjåsjön , Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459692.2506225323</v>
+        <v>460373</v>
       </c>
       <c r="R39" t="n">
-        <v>6864358.898972569</v>
+        <v>6864137</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4902,22 +4360,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4932,27 +4380,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>100711294</v>
+        <v>100711293</v>
       </c>
       <c r="B40" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4960,21 +4403,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4984,10 +4427,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459713.0093013519</v>
+        <v>460327</v>
       </c>
       <c r="R40" t="n">
-        <v>6864997.60001069</v>
+        <v>6864101</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5017,19 +4460,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5056,15 +4489,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>100711287</v>
+        <v>100711267</v>
       </c>
       <c r="B41" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5072,21 +4500,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5096,10 +4524,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459787.0113399865</v>
+        <v>460327</v>
       </c>
       <c r="R41" t="n">
-        <v>6864590.56685351</v>
+        <v>6864101</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5129,19 +4557,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5168,37 +4586,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>100711263</v>
+        <v>100711320</v>
       </c>
       <c r="B42" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5208,10 +4621,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459735.9482922081</v>
+        <v>459838</v>
       </c>
       <c r="R42" t="n">
-        <v>6864942.203522061</v>
+        <v>6864538</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5241,19 +4654,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5280,15 +4683,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>100711275</v>
+        <v>118970248</v>
       </c>
       <c r="B43" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5296,37 +4694,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459931.2134978434</v>
+        <v>459807</v>
       </c>
       <c r="R43" t="n">
-        <v>6864010.645513522</v>
+        <v>6864187</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5350,22 +4748,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På kolbotten.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5380,27 +4773,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>100711276</v>
+        <v>96205090</v>
       </c>
       <c r="B44" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5408,37 +4796,44 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Kvarnbergsmyren, Härjåsjön, Lillhärdal, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459695.4964385364</v>
+        <v>459823</v>
       </c>
       <c r="R44" t="n">
-        <v>6864473.842062026</v>
+        <v>6864806</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5462,22 +4857,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i laven</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5486,33 +4876,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>100711286</v>
+        <v>96205253</v>
       </c>
       <c r="B45" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5520,37 +4906,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Kvarnbergsmyren, Härjåsjön, Lillhärdal, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459735.9316082247</v>
+        <v>459689</v>
       </c>
       <c r="R45" t="n">
-        <v>6864940.790230161</v>
+        <v>6864623</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5574,22 +4963,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på och i anslutning till viltstig</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5598,71 +4982,77 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>100711320</v>
+        <v>118970206</v>
       </c>
       <c r="B46" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2869</v>
+        <v>4366</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459837.8383123052</v>
+        <v>459768</v>
       </c>
       <c r="R46" t="n">
-        <v>6864538.60567635</v>
+        <v>6864215</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5686,22 +5076,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5716,27 +5096,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>100711266</v>
+        <v>118970344</v>
       </c>
       <c r="B47" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5744,37 +5119,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459784.8725669582</v>
+        <v>459773</v>
       </c>
       <c r="R47" t="n">
-        <v>6865089.568225338</v>
+        <v>6864317</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5798,22 +5173,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5828,27 +5193,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118970248</v>
+        <v>118970354</v>
       </c>
       <c r="B48" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5856,21 +5216,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5880,10 +5240,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459807</v>
+        <v>459784</v>
       </c>
       <c r="R48" t="n">
-        <v>6864187</v>
+        <v>6864314</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5916,11 +5276,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På kolbotten.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5947,19 +5302,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118970344</v>
+        <v>118970679</v>
       </c>
       <c r="B49" t="n">
-        <v>91821</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5983,14 +5333,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459773</v>
+        <v>459803</v>
       </c>
       <c r="R49" t="n">
-        <v>6864317</v>
+        <v>6864527</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6049,50 +5399,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118970206</v>
+        <v>118970438</v>
       </c>
       <c r="B50" t="n">
-        <v>91821</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459768</v>
+        <v>459589</v>
       </c>
       <c r="R50" t="n">
-        <v>6864215</v>
+        <v>6864328</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6151,53 +5496,55 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118970679</v>
+        <v>96205216</v>
       </c>
       <c r="B51" t="n">
-        <v>91821</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Kvarnbergsmyren, Härjåsjön, Lillhärdal, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459803</v>
+        <v>459807</v>
       </c>
       <c r="R51" t="n">
-        <v>6864527</v>
+        <v>6864565</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6221,12 +5568,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6235,33 +5582,39 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118970157</v>
+        <v>98951677</v>
       </c>
       <c r="B52" t="n">
-        <v>78247</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6269,37 +5622,38 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459817</v>
+        <v>459692</v>
       </c>
       <c r="R52" t="n">
-        <v>6864172</v>
+        <v>6864359</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6323,12 +5677,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6355,15 +5709,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118970438</v>
+        <v>118970157</v>
       </c>
       <c r="B53" t="n">
-        <v>91432</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6371,34 +5720,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4745</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459589</v>
+        <v>459817</v>
       </c>
       <c r="R53" t="n">
-        <v>6864328</v>
+        <v>6864172</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6457,53 +5806,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118970354</v>
+        <v>100711263</v>
       </c>
       <c r="B54" t="n">
-        <v>91821</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459784</v>
+        <v>459736</v>
       </c>
       <c r="R54" t="n">
-        <v>6864314</v>
+        <v>6864942</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6527,12 +5871,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6547,15 +5891,797 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>100711294</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>..., Hjd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>459713</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6864998</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>98951687</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Härjåsjön, Hjd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>459662</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6864606</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-02-28</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-02-28</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
           <t>lennart karlsson</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
+      <c r="AX56" t="inlineStr">
         <is>
           <t>lennart karlsson</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>100711271</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>..., Hjd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>459931</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6864011</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Höna</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>100711275</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>..., Hjd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>459931</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6864011</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>100711276</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>..., Hjd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>459696</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6864474</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>100711286</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>..., Hjd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>459736</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6864941</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>100711287</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>..., Hjd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>459787</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6864591</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>100711266</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>..., Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>459785</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6865090</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
